--- a/outputs/tucker-ga-rfp-2026-008-row-maintenance.matrix.xlsx
+++ b/outputs/tucker-ga-rfp-2026-008-row-maintenance.matrix.xlsx
@@ -462,7 +462,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Evaluation matrix — City of Tucker Request for Proposal [p2:1] — stated total 100 — sum 100</t>
+          <t>Evaluation matrix — RFP 2026-008 [p1:4] — stated total 100 — sum 100</t>
         </is>
       </c>
     </row>

--- a/outputs/tucker-ga-rfp-2026-008-row-maintenance.matrix.xlsx
+++ b/outputs/tucker-ga-rfp-2026-008-row-maintenance.matrix.xlsx
@@ -560,15 +560,11 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>3. Describe the company’s understanding of the proposed services as described in the Scope of Work. [p13:14-p13:15]</t>
+          <t>not in source</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>draft: write the response to this criterion from the inputs in Input needed, citing each one</t>
-        </is>
-      </c>
+      <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -608,15 +604,11 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>5. List and describe company experience in the past five years that best matches the Scope of Work. [p13:25-p13:26]</t>
+          <t>not in source</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>draft: write the response to this criterion from the inputs in Input needed, citing each one</t>
-        </is>
-      </c>
+      <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -651,20 +643,16 @@
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>The contract award will include an annual Not-to-Exceed amount to be determined by the City of Tucker based on the rates provided. [p14:30-p14:31]</t>
+          <t>In scoring against stated criteria, the City may consider such factors as accepted industry standards and a comparative evaluation of all other qualified RFP responses in terms of differing price, quality, and contractual factors. [p13:35-p13:38]</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>6. Submit the required forms provided as part of the bid package, which will not be counted toward the 15-page limit. [p13:30-p13:31]</t>
+          <t>Cost Proposal (form provided) [p3:11]</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>assemble: fill the RFP's own form from figures a person supplies; no prose</t>
-        </is>
-      </c>
+      <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>

--- a/outputs/tucker-ga-rfp-2026-008-row-maintenance.matrix.xlsx
+++ b/outputs/tucker-ga-rfp-2026-008-row-maintenance.matrix.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evaluation Matrix'!$A$2:$L$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +28,10 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,19 +66,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,21 +445,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,215 +466,162 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RFP section</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>RFP criterion (their words)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Points</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Input needed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Input data source</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Evaluation criteria (what the scorer looks for)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Proposal section that answers it</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Claude does</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Human check</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>4. Selection Criteria [p14:8]</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Proposed Management Plan and Approach [p14:15]</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Each proposer should include a summary of their proposed management plan. The management plan should describe the number of crews and seasonal personnel, if any, proposed to accomplish the required work. [p13:14-p13:17]</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>The proposal shall outline the plan that the company will use to provide the most effective delivery of the requested services as outlined in the Scope of Work. [p14:16-p14:17]</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>not in source</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>From the RFP section: 4. Selection Criteria [p14:8]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>4. Selection Criteria [p14:8]</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Qualifications and Similar Project Experience of the Company and Staff [p14:19]</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Provide information on supervisory personnel to be assigned to this contract, including for the project superintendent, road maintenance foreman, and stormwater foreman The proposal should identify any applicable certifications held by key personnel who will perform the work. Provide copies of appropriate required licenses. [p13:19-p13:23]</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>The proposal must give a detailed report of related experiences that demonstrate the ability of the proposer to perform requested services as outlined in the Scope of Work. The proposal shall include sufficient information to indicate the abilities, qualifications, and experience of all persons who would be assigned to provide the required services. [p14:21-p14:25]</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>not in source</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>open</t>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>What the RFP will score (their exact words)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Points for this item</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>What the RFP asks you to provide</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Where your team will get it</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>What the scorer will look for</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Where it goes in your proposal</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Lead for this section</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer for this section</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4. Selection Criteria [p14:8]</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Cost Proposal [p14:27]</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Proposers shall provide lump sum costs for basic services per the Cost Proposal Form provided. Proposers shall also submit the Unit Cost Schedule per the form provided. [p14:28-p14:30]</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>1. Proposed Management Plan and Approach [p14:15]</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Each proposer should include a summary of their proposed management plan. The management plan should describe the number of crews and seasonal personnel, if any, proposed to accomplish the required work. [p13:14-p13:17]</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>The proposal shall outline the plan that the company will use to provide the most effective delivery of the requested services as outlined in the Scope of Work. [p14:16-p14:17]</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>In scoring against stated criteria, the City may consider such factors as accepted industry standards and a comparative evaluation of all other qualified RFP responses in terms of differing price, quality, and contractual factors. [p13:35-p13:38]</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Cost Proposal (form provided) [p3:11]</t>
-        </is>
-      </c>
+          <t>not in source</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="C6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2. Qualifications and Similar Project Experience of the Company and Staff [p14:19]</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Provide information on supervisory personnel to be assigned to this contract, including for the project superintendent, road maintenance foreman, and stormwater foreman The proposal should identify any applicable certifications held by key personnel who will perform the work. Provide copies of appropriate required licenses. [p13:19-p13:23]</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>The proposal must give a detailed report of related experiences that demonstrate the ability of the proposer to perform requested services as outlined in the Scope of Work. The proposal shall include sufficient information to indicate the abilities, qualifications, and experience of all persons who would be assigned to provide the required services. [p14:21-p14:25]</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>not in source</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>3. Cost Proposal [p14:27]</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Proposers shall provide lump sum costs for basic services per the Cost Proposal Form provided. Proposers shall also submit the Unit Cost Schedule per the form provided. [p14:28-p14:30]</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>In scoring against stated criteria, the City may consider such factors as accepted industry standards and a comparative evaluation of all other qualified RFP responses in terms of differing price, quality, and contractual factors. [p13:35-p13:38]</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Cost Proposal (form provided) [p3:11]</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D6" s="5">
-        <f>SUM(D3:D5)</f>
+      <c r="C9" s="6">
+        <f>C5+C6+C7</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L5"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
